--- a/F429引脚统计.xlsx
+++ b/F429引脚统计.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20338"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20411"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E886449C-21B5-4AE6-9A1E-DE5F0A111F2C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09A674C-37FA-44D7-B90A-B2BFD4469260}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -947,7 +947,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -974,13 +974,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -997,7 +991,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1020,9 +1014,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1035,9 +1026,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1047,25 +1035,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1349,23 +1340,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N66"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" style="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="1"/>
     <col min="7" max="7" width="9" style="5"/>
-    <col min="8" max="8" width="20.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.6640625" style="1" customWidth="1"/>
     <col min="9" max="10" width="9" style="1"/>
-    <col min="11" max="11" width="21.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="21.109375" style="1" customWidth="1"/>
     <col min="12" max="13" width="9" style="1"/>
-    <col min="14" max="14" width="15.125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.109375" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1400,11 +1391,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -1420,28 +1411,28 @@
         <v>0</v>
       </c>
       <c r="G2" s="6"/>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="L2" s="10">
-        <v>1</v>
-      </c>
-      <c r="M2" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+      <c r="L2" s="9">
+        <v>1</v>
+      </c>
+      <c r="M2" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
       <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
@@ -1455,24 +1446,24 @@
         <v>0</v>
       </c>
       <c r="G3" s="6"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="10" t="s">
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="L3" s="10">
-        <v>1</v>
-      </c>
-      <c r="M3" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
+      <c r="L3" s="9">
+        <v>1</v>
+      </c>
+      <c r="M3" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
       <c r="C4" s="4" t="s">
         <v>10</v>
       </c>
@@ -1486,10 +1477,10 @@
         <v>0</v>
       </c>
       <c r="G4" s="6"/>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="15" t="s">
         <v>103</v>
       </c>
       <c r="J4" s="7" t="s">
@@ -1504,13 +1495,13 @@
       <c r="M4" s="7">
         <v>0</v>
       </c>
-      <c r="N4" s="22" t="s">
+      <c r="N4" s="15" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
       <c r="C5" s="4" t="s">
         <v>12</v>
       </c>
@@ -1524,8 +1515,8 @@
         <v>2</v>
       </c>
       <c r="G5" s="6"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
       <c r="J5" s="7" t="s">
         <v>126</v>
       </c>
@@ -1538,11 +1529,11 @@
       <c r="M5" s="7">
         <v>0</v>
       </c>
-      <c r="N5" s="22"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
+      <c r="N5" s="15"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
       <c r="C6" s="4" t="s">
         <v>14</v>
       </c>
@@ -1556,10 +1547,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="6"/>
-      <c r="H6" s="20" t="s">
+      <c r="H6" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="17" t="s">
         <v>83</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -1575,9 +1566,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
       <c r="C7" s="4" t="s">
         <v>16</v>
       </c>
@@ -1591,8 +1582,8 @@
         <v>0</v>
       </c>
       <c r="G7" s="6"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
       <c r="J7" s="1" t="s">
         <v>85</v>
       </c>
@@ -1606,134 +1597,134 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="18" t="s">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="8">
-        <v>1</v>
-      </c>
-      <c r="F8" s="8">
+      <c r="E8" s="21">
+        <v>1</v>
+      </c>
+      <c r="F8" s="21">
         <v>2</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="I8" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="J8" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="K8" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="L8" s="12">
-        <v>1</v>
-      </c>
-      <c r="M8" s="12">
-        <v>0</v>
-      </c>
-      <c r="N8" s="23" t="s">
+      <c r="L8" s="11">
+        <v>1</v>
+      </c>
+      <c r="M8" s="11">
+        <v>0</v>
+      </c>
+      <c r="N8" s="18" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="8" t="s">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="8">
-        <v>1</v>
-      </c>
-      <c r="F9" s="8">
-        <v>0</v>
-      </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="12" t="s">
+      <c r="E9" s="21">
+        <v>1</v>
+      </c>
+      <c r="F9" s="21">
+        <v>0</v>
+      </c>
+      <c r="G9" s="22"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="K9" s="12" t="s">
+      <c r="K9" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="L9" s="12">
-        <v>1</v>
-      </c>
-      <c r="M9" s="12">
-        <v>0</v>
-      </c>
-      <c r="N9" s="23"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="8" t="s">
+      <c r="L9" s="11">
+        <v>1</v>
+      </c>
+      <c r="M9" s="11">
+        <v>0</v>
+      </c>
+      <c r="N9" s="18"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="8">
-        <v>1</v>
-      </c>
-      <c r="F10" s="8">
-        <v>0</v>
-      </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="12" t="s">
+      <c r="E10" s="21">
+        <v>1</v>
+      </c>
+      <c r="F10" s="21">
+        <v>0</v>
+      </c>
+      <c r="G10" s="22"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="L10" s="12">
-        <v>1</v>
-      </c>
-      <c r="M10" s="12">
+      <c r="L10" s="11">
+        <v>1</v>
+      </c>
+      <c r="M10" s="11">
         <v>2</v>
       </c>
-      <c r="N10" s="23"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="8" t="s">
+      <c r="N10" s="18"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="8">
-        <v>1</v>
-      </c>
-      <c r="F11" s="8">
-        <v>0</v>
-      </c>
-      <c r="G11" s="19"/>
-      <c r="H11" s="20" t="s">
+      <c r="E11" s="21">
+        <v>1</v>
+      </c>
+      <c r="F11" s="21">
+        <v>0</v>
+      </c>
+      <c r="G11" s="22"/>
+      <c r="H11" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="17" t="s">
         <v>93</v>
       </c>
       <c r="J11" s="1" t="s">
@@ -1749,24 +1740,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="13" t="s">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="8">
-        <v>1</v>
-      </c>
-      <c r="F12" s="8">
-        <v>0</v>
-      </c>
-      <c r="G12" s="19"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
+      <c r="E12" s="21">
+        <v>1</v>
+      </c>
+      <c r="F12" s="21">
+        <v>0</v>
+      </c>
+      <c r="G12" s="22"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
       <c r="J12" s="1" t="s">
         <v>95</v>
       </c>
@@ -1780,123 +1771,123 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="13" t="s">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="8">
-        <v>1</v>
-      </c>
-      <c r="F13" s="8">
-        <v>0</v>
-      </c>
-      <c r="G13" s="19"/>
-      <c r="H13" s="21" t="s">
+      <c r="E13" s="21">
+        <v>1</v>
+      </c>
+      <c r="F13" s="21">
+        <v>0</v>
+      </c>
+      <c r="G13" s="22"/>
+      <c r="H13" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="I13" s="21" t="s">
+      <c r="I13" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="L13" s="11">
-        <v>1</v>
-      </c>
-      <c r="M13" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="13" t="s">
+      <c r="L13" s="10">
+        <v>1</v>
+      </c>
+      <c r="M13" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="8">
-        <v>1</v>
-      </c>
-      <c r="F14" s="8">
-        <v>0</v>
-      </c>
-      <c r="G14" s="19"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="11" t="s">
+      <c r="E14" s="21">
+        <v>1</v>
+      </c>
+      <c r="F14" s="21">
+        <v>0</v>
+      </c>
+      <c r="G14" s="22"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="L14" s="11">
-        <v>1</v>
-      </c>
-      <c r="M14" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="13" t="s">
+      <c r="L14" s="10">
+        <v>1</v>
+      </c>
+      <c r="M14" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="E15" s="8">
-        <v>1</v>
-      </c>
-      <c r="F15" s="8">
-        <v>0</v>
-      </c>
-      <c r="G15" s="19"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="11" t="s">
+      <c r="E15" s="21">
+        <v>1</v>
+      </c>
+      <c r="F15" s="21">
+        <v>0</v>
+      </c>
+      <c r="G15" s="22"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="K15" s="11" t="s">
+      <c r="K15" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="L15" s="11">
-        <v>1</v>
-      </c>
-      <c r="M15" s="11">
+      <c r="L15" s="10">
+        <v>1</v>
+      </c>
+      <c r="M15" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="13" t="s">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="8">
-        <v>1</v>
-      </c>
-      <c r="F16" s="8">
-        <v>0</v>
-      </c>
-      <c r="G16" s="19"/>
-      <c r="H16" s="17" t="s">
+      <c r="E16" s="21">
+        <v>1</v>
+      </c>
+      <c r="F16" s="21">
+        <v>0</v>
+      </c>
+      <c r="G16" s="22"/>
+      <c r="H16" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="I16" s="17" t="s">
+      <c r="I16" s="16" t="s">
         <v>129</v>
       </c>
       <c r="J16" s="4" t="s">
@@ -1912,24 +1903,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="13" t="s">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="8">
-        <v>1</v>
-      </c>
-      <c r="F17" s="8">
-        <v>0</v>
-      </c>
-      <c r="G17" s="19"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
+      <c r="E17" s="21">
+        <v>1</v>
+      </c>
+      <c r="F17" s="21">
+        <v>0</v>
+      </c>
+      <c r="G17" s="22"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
       <c r="J17" s="4" t="s">
         <v>132</v>
       </c>
@@ -1943,29 +1934,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" s="17" t="s">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="21">
         <v>2</v>
       </c>
-      <c r="G18" s="17" t="s">
+      <c r="G18" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="H18" s="20" t="s">
+      <c r="H18" s="17" t="s">
         <v>105</v>
       </c>
       <c r="I18" s="3" t="s">
@@ -1984,23 +1975,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="15" t="s">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="E19" s="15">
-        <v>1</v>
-      </c>
-      <c r="F19" s="15">
-        <v>0</v>
-      </c>
-      <c r="G19" s="17"/>
-      <c r="H19" s="20"/>
+      <c r="E19" s="21">
+        <v>1</v>
+      </c>
+      <c r="F19" s="21">
+        <v>0</v>
+      </c>
+      <c r="G19" s="20"/>
+      <c r="H19" s="17"/>
       <c r="I19" s="3" t="s">
         <v>145</v>
       </c>
@@ -2017,22 +2008,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="15" t="s">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="F20" s="15">
-        <v>0</v>
-      </c>
-      <c r="G20" s="17"/>
+      <c r="F20" s="21">
+        <v>0</v>
+      </c>
+      <c r="G20" s="20"/>
       <c r="H20" s="4" t="s">
         <v>106</v>
       </c>
@@ -2055,95 +2046,95 @@
         <v>146</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="15" t="s">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="E21" s="15">
-        <v>1</v>
-      </c>
-      <c r="F21" s="15">
-        <v>0</v>
-      </c>
-      <c r="G21" s="17"/>
-      <c r="H21" s="9" t="s">
+      <c r="E21" s="21">
+        <v>1</v>
+      </c>
+      <c r="F21" s="21">
+        <v>0</v>
+      </c>
+      <c r="G21" s="20"/>
+      <c r="H21" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
       <c r="N21" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="15" t="s">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="E22" s="15">
-        <v>1</v>
-      </c>
-      <c r="F22" s="15">
-        <v>0</v>
-      </c>
-      <c r="G22" s="17"/>
+      <c r="E22" s="21">
+        <v>1</v>
+      </c>
+      <c r="F22" s="21">
+        <v>0</v>
+      </c>
+      <c r="G22" s="20"/>
       <c r="I22" s="1" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="15" t="s">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="15">
-        <v>1</v>
-      </c>
-      <c r="F23" s="15">
-        <v>0</v>
-      </c>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17" t="s">
+      <c r="E23" s="21">
+        <v>1</v>
+      </c>
+      <c r="F23" s="21">
+        <v>0</v>
+      </c>
+      <c r="G23" s="20"/>
+      <c r="H23" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="I23" s="17" t="s">
+      <c r="I23" s="16" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="24" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15" t="s">
+    <row r="24" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15" t="s">
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
       <c r="J24" s="4" t="s">
         <v>117</v>
       </c>
@@ -2157,28 +2148,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="17" t="s">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="9">
-        <v>1</v>
-      </c>
-      <c r="F25" s="9">
+      <c r="E25" s="8">
+        <v>1</v>
+      </c>
+      <c r="F25" s="8">
         <v>2</v>
       </c>
-      <c r="G25" s="9"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
       <c r="J25" s="4" t="s">
         <v>118</v>
       </c>
@@ -2192,160 +2183,160 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="9" t="s">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E26" s="9">
-        <v>1</v>
-      </c>
-      <c r="F26" s="9">
-        <v>0</v>
-      </c>
-      <c r="G26" s="9"/>
-      <c r="H26" s="17" t="s">
+      <c r="E26" s="8">
+        <v>1</v>
+      </c>
+      <c r="F26" s="8">
+        <v>0</v>
+      </c>
+      <c r="G26" s="8"/>
+      <c r="H26" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="I26" s="17" t="s">
+      <c r="I26" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="J26" s="9" t="s">
+      <c r="J26" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="K26" s="9" t="s">
+      <c r="K26" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="L26" s="9">
-        <v>1</v>
-      </c>
-      <c r="M26" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="9" t="s">
+      <c r="L26" s="8">
+        <v>1</v>
+      </c>
+      <c r="M26" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E27" s="9">
-        <v>1</v>
-      </c>
-      <c r="F27" s="9">
-        <v>0</v>
-      </c>
-      <c r="G27" s="9"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="9" t="s">
+      <c r="E27" s="8">
+        <v>1</v>
+      </c>
+      <c r="F27" s="8">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="K27" s="9" t="s">
+      <c r="K27" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="L27" s="9">
-        <v>1</v>
-      </c>
-      <c r="M27" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="9" t="s">
+      <c r="L27" s="8">
+        <v>1</v>
+      </c>
+      <c r="M27" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E28" s="9">
-        <v>1</v>
-      </c>
-      <c r="F28" s="9">
-        <v>0</v>
-      </c>
-      <c r="G28" s="9"/>
-      <c r="H28" s="17" t="s">
+      <c r="E28" s="8">
+        <v>1</v>
+      </c>
+      <c r="F28" s="8">
+        <v>0</v>
+      </c>
+      <c r="G28" s="8"/>
+      <c r="H28" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10" t="s">
+      <c r="I28" s="9"/>
+      <c r="J28" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="K28" s="10" t="s">
+      <c r="K28" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="9" t="s">
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E29" s="9">
-        <v>1</v>
-      </c>
-      <c r="F29" s="9">
-        <v>0</v>
-      </c>
-      <c r="G29" s="9"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10" t="s">
+      <c r="E29" s="8">
+        <v>1</v>
+      </c>
+      <c r="F29" s="8">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="K29" s="10" t="s">
+      <c r="K29" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="9" t="s">
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="E30" s="9">
-        <v>1</v>
-      </c>
-      <c r="F30" s="9">
-        <v>0</v>
-      </c>
-      <c r="G30" s="9"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10" t="s">
+      <c r="E30" s="8">
+        <v>1</v>
+      </c>
+      <c r="F30" s="8">
+        <v>0</v>
+      </c>
+      <c r="G30" s="8"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="K30" s="10" t="s">
+      <c r="K30" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A31" s="20" t="s">
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B31" s="20" t="s">
+      <c r="B31" s="17" t="s">
         <v>65</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -2360,20 +2351,20 @@
       <c r="F31" s="1">
         <v>2</v>
       </c>
-      <c r="H31" s="17"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10" t="s">
+      <c r="H31" s="16"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="K31" s="10" t="s">
+      <c r="K31" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
       <c r="C32" s="1" t="s">
         <v>72</v>
       </c>
@@ -2386,20 +2377,20 @@
       <c r="F32" s="1">
         <v>0</v>
       </c>
-      <c r="H32" s="17"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10" t="s">
+      <c r="H32" s="16"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="K32" s="10" t="s">
+      <c r="K32" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A33" s="20"/>
-      <c r="B33" s="20"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
       <c r="C33" s="1" t="s">
         <v>73</v>
       </c>
@@ -2412,20 +2403,20 @@
       <c r="F33" s="1">
         <v>0</v>
       </c>
-      <c r="H33" s="17"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10" t="s">
+      <c r="H33" s="16"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="K33" s="10" t="s">
+      <c r="K33" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A34" s="20"/>
-      <c r="B34" s="20"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
       <c r="C34" s="1" t="s">
         <v>74</v>
       </c>
@@ -2438,427 +2429,407 @@
       <c r="F34" s="1">
         <v>0</v>
       </c>
-      <c r="H34" s="17"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10" t="s">
+      <c r="H34" s="16"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="K34" s="10" t="s">
+      <c r="K34" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10" t="s">
+      <c r="H35" s="16"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="K35" s="10" t="s">
+      <c r="K35" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10" t="s">
+      <c r="H36" s="16"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="K36" s="10" t="s">
+      <c r="K36" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="H37" s="17"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10" t="s">
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H37" s="16"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="K37" s="10" t="s">
+      <c r="K37" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="H38" s="17"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10" t="s">
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H38" s="16"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="K38" s="10" t="s">
+      <c r="K38" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="H39" s="17"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10" t="s">
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H39" s="16"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="K39" s="10" t="s">
+      <c r="K39" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="H40" s="17"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10" t="s">
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H40" s="16"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="K40" s="10" t="s">
+      <c r="K40" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="H41" s="17"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10" t="s">
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H41" s="16"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="K41" s="10" t="s">
+      <c r="K41" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="H42" s="17"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10" t="s">
+      <c r="L41" s="9"/>
+      <c r="M41" s="9"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H42" s="16"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="K42" s="10" t="s">
+      <c r="K42" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="L42" s="10"/>
-      <c r="M42" s="10"/>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="H43" s="17"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10" t="s">
+      <c r="L42" s="9"/>
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H43" s="16"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="K43" s="10" t="s">
+      <c r="K43" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="H44" s="17"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10" t="s">
+      <c r="L43" s="9"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H44" s="16"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="K44" s="10" t="s">
+      <c r="K44" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="H45" s="17"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10" t="s">
+      <c r="L44" s="9"/>
+      <c r="M44" s="9"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H45" s="16"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="K45" s="10" t="s">
+      <c r="K45" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="H46" s="17"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10" t="s">
+      <c r="L45" s="9"/>
+      <c r="M45" s="9"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H46" s="16"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="K46" s="10" t="s">
+      <c r="K46" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="H47" s="17"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10" t="s">
+      <c r="L46" s="9"/>
+      <c r="M46" s="9"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H47" s="16"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="K47" s="10" t="s">
+      <c r="K47" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="H48" s="17"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10" t="s">
+      <c r="L47" s="9"/>
+      <c r="M47" s="9"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H48" s="16"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="K48" s="10" t="s">
+      <c r="K48" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
-    </row>
-    <row r="49" spans="8:13" x14ac:dyDescent="0.2">
-      <c r="H49" s="17"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10" t="s">
+      <c r="L48" s="9"/>
+      <c r="M48" s="9"/>
+    </row>
+    <row r="49" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H49" s="16"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="K49" s="10" t="s">
+      <c r="K49" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="L49" s="10"/>
-      <c r="M49" s="10"/>
-    </row>
-    <row r="50" spans="8:13" x14ac:dyDescent="0.2">
-      <c r="H50" s="17"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10" t="s">
+      <c r="L49" s="9"/>
+      <c r="M49" s="9"/>
+    </row>
+    <row r="50" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H50" s="16"/>
+      <c r="I50" s="9"/>
+      <c r="J50" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="K50" s="10" t="s">
+      <c r="K50" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="L50" s="10"/>
-      <c r="M50" s="10"/>
-    </row>
-    <row r="51" spans="8:13" x14ac:dyDescent="0.2">
-      <c r="H51" s="17"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10" t="s">
+      <c r="L50" s="9"/>
+      <c r="M50" s="9"/>
+    </row>
+    <row r="51" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H51" s="16"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="K51" s="10" t="s">
+      <c r="K51" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
-    </row>
-    <row r="52" spans="8:13" x14ac:dyDescent="0.2">
-      <c r="H52" s="17"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10" t="s">
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
+    </row>
+    <row r="52" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H52" s="16"/>
+      <c r="I52" s="9"/>
+      <c r="J52" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="K52" s="10" t="s">
+      <c r="K52" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="L52" s="10"/>
-      <c r="M52" s="10"/>
-    </row>
-    <row r="53" spans="8:13" x14ac:dyDescent="0.2">
-      <c r="H53" s="17"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10" t="s">
+      <c r="L52" s="9"/>
+      <c r="M52" s="9"/>
+    </row>
+    <row r="53" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H53" s="16"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="K53" s="10" t="s">
+      <c r="K53" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
-    </row>
-    <row r="54" spans="8:13" x14ac:dyDescent="0.2">
-      <c r="H54" s="17"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10" t="s">
+      <c r="L53" s="9"/>
+      <c r="M53" s="9"/>
+    </row>
+    <row r="54" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H54" s="16"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="K54" s="10" t="s">
+      <c r="K54" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
-    </row>
-    <row r="55" spans="8:13" x14ac:dyDescent="0.2">
-      <c r="H55" s="17"/>
-      <c r="I55" s="10"/>
-      <c r="J55" s="10" t="s">
+      <c r="L54" s="9"/>
+      <c r="M54" s="9"/>
+    </row>
+    <row r="55" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H55" s="16"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="K55" s="10" t="s">
+      <c r="K55" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="L55" s="10"/>
-      <c r="M55" s="10"/>
-    </row>
-    <row r="56" spans="8:13" x14ac:dyDescent="0.2">
-      <c r="H56" s="17"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10" t="s">
+      <c r="L55" s="9"/>
+      <c r="M55" s="9"/>
+    </row>
+    <row r="56" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H56" s="16"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="K56" s="10" t="s">
+      <c r="K56" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="L56" s="10"/>
-      <c r="M56" s="10"/>
-    </row>
-    <row r="57" spans="8:13" x14ac:dyDescent="0.2">
-      <c r="H57" s="17"/>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10" t="s">
+      <c r="L56" s="9"/>
+      <c r="M56" s="9"/>
+    </row>
+    <row r="57" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H57" s="16"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="K57" s="10" t="s">
+      <c r="K57" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="L57" s="10"/>
-      <c r="M57" s="10"/>
-    </row>
-    <row r="58" spans="8:13" x14ac:dyDescent="0.2">
-      <c r="H58" s="17"/>
-      <c r="I58" s="10"/>
-      <c r="J58" s="10" t="s">
+      <c r="L57" s="9"/>
+      <c r="M57" s="9"/>
+    </row>
+    <row r="58" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H58" s="16"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="K58" s="10" t="s">
+      <c r="K58" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="L58" s="10"/>
-      <c r="M58" s="10"/>
-    </row>
-    <row r="59" spans="8:13" x14ac:dyDescent="0.2">
-      <c r="H59" s="17"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10" t="s">
+      <c r="L58" s="9"/>
+      <c r="M58" s="9"/>
+    </row>
+    <row r="59" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H59" s="16"/>
+      <c r="I59" s="9"/>
+      <c r="J59" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="K59" s="10" t="s">
+      <c r="K59" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="L59" s="10"/>
-      <c r="M59" s="10"/>
-    </row>
-    <row r="60" spans="8:13" x14ac:dyDescent="0.2">
-      <c r="H60" s="17"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="10" t="s">
+      <c r="L59" s="9"/>
+      <c r="M59" s="9"/>
+    </row>
+    <row r="60" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H60" s="16"/>
+      <c r="I60" s="9"/>
+      <c r="J60" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="K60" s="10" t="s">
+      <c r="K60" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="L60" s="10"/>
-      <c r="M60" s="10"/>
-    </row>
-    <row r="61" spans="8:13" x14ac:dyDescent="0.2">
-      <c r="H61" s="17"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10" t="s">
+      <c r="L60" s="9"/>
+      <c r="M60" s="9"/>
+    </row>
+    <row r="61" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H61" s="16"/>
+      <c r="I61" s="9"/>
+      <c r="J61" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="K61" s="10" t="s">
+      <c r="K61" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="L61" s="10"/>
-      <c r="M61" s="10"/>
-    </row>
-    <row r="62" spans="8:13" x14ac:dyDescent="0.2">
-      <c r="H62" s="17"/>
-      <c r="I62" s="10"/>
-      <c r="J62" s="10" t="s">
+      <c r="L61" s="9"/>
+      <c r="M61" s="9"/>
+    </row>
+    <row r="62" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H62" s="16"/>
+      <c r="I62" s="9"/>
+      <c r="J62" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="K62" s="10" t="s">
+      <c r="K62" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="L62" s="10"/>
-      <c r="M62" s="10"/>
-    </row>
-    <row r="63" spans="8:13" x14ac:dyDescent="0.2">
-      <c r="H63" s="17"/>
-      <c r="I63" s="10"/>
-      <c r="J63" s="10" t="s">
+      <c r="L62" s="9"/>
+      <c r="M62" s="9"/>
+    </row>
+    <row r="63" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H63" s="16"/>
+      <c r="I63" s="9"/>
+      <c r="J63" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="K63" s="14" t="s">
+      <c r="K63" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="L63" s="10"/>
-      <c r="M63" s="10"/>
-    </row>
-    <row r="64" spans="8:13" x14ac:dyDescent="0.2">
-      <c r="H64" s="17"/>
-      <c r="I64" s="10"/>
-      <c r="J64" s="10" t="s">
+      <c r="L63" s="9"/>
+      <c r="M63" s="9"/>
+    </row>
+    <row r="64" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H64" s="16"/>
+      <c r="I64" s="9"/>
+      <c r="J64" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="K64" s="10" t="s">
+      <c r="K64" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="L64" s="10"/>
-      <c r="M64" s="10"/>
-    </row>
-    <row r="65" spans="8:13" x14ac:dyDescent="0.2">
-      <c r="H65" s="17"/>
-      <c r="I65" s="10"/>
-      <c r="J65" s="10" t="s">
+      <c r="L64" s="9"/>
+      <c r="M64" s="9"/>
+    </row>
+    <row r="65" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H65" s="16"/>
+      <c r="I65" s="9"/>
+      <c r="J65" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="K65" s="10" t="s">
+      <c r="K65" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="L65" s="10"/>
-      <c r="M65" s="10"/>
-    </row>
-    <row r="66" spans="8:13" x14ac:dyDescent="0.2">
-      <c r="H66" s="17"/>
-      <c r="I66" s="10"/>
-      <c r="J66" s="10" t="s">
+      <c r="L65" s="9"/>
+      <c r="M65" s="9"/>
+    </row>
+    <row r="66" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H66" s="16"/>
+      <c r="I66" s="9"/>
+      <c r="J66" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="K66" s="10" t="s">
+      <c r="K66" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="L66" s="10"/>
-      <c r="M66" s="10"/>
+      <c r="L66" s="9"/>
+      <c r="M66" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="G18:G23"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="I8:I10"/>
-    <mergeCell ref="H8:H10"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="N8:N10"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I13:I15"/>
-    <mergeCell ref="H13:H15"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="H23:H25"/>
-    <mergeCell ref="I23:I25"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="H16:H17"/>
     <mergeCell ref="H28:H66"/>
     <mergeCell ref="B2:B7"/>
     <mergeCell ref="A2:A7"/>
@@ -2873,6 +2844,26 @@
     <mergeCell ref="B31:B34"/>
     <mergeCell ref="A31:A34"/>
     <mergeCell ref="H26:H27"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I13:I15"/>
+    <mergeCell ref="H13:H15"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="H23:H25"/>
+    <mergeCell ref="I23:I25"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="G18:G23"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="I8:I10"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="N8:N10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
